--- a/models_guided/codebooks.xlsx
+++ b/models_guided/codebooks.xlsx
@@ -416,58 +416,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:BM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="12" customWidth="1" min="44" max="44"/>
-    <col width="12" customWidth="1" min="45" max="45"/>
-    <col width="12" customWidth="1" min="46" max="46"/>
-    <col width="12" customWidth="1" min="47" max="47"/>
-    <col width="12" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -620,6 +636,54 @@
       <c r="AW1" t="n">
         <v>47</v>
       </c>
+      <c r="AX1" t="n">
+        <v>48</v>
+      </c>
+      <c r="AY1" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ1" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA1" t="n">
+        <v>51</v>
+      </c>
+      <c r="BB1" t="n">
+        <v>52</v>
+      </c>
+      <c r="BC1" t="n">
+        <v>53</v>
+      </c>
+      <c r="BD1" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE1" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF1" t="n">
+        <v>56</v>
+      </c>
+      <c r="BG1" t="n">
+        <v>57</v>
+      </c>
+      <c r="BH1" t="n">
+        <v>58</v>
+      </c>
+      <c r="BI1" t="n">
+        <v>59</v>
+      </c>
+      <c r="BJ1" t="n">
+        <v>60</v>
+      </c>
+      <c r="BK1" t="n">
+        <v>61</v>
+      </c>
+      <c r="BL1" t="n">
+        <v>62</v>
+      </c>
+      <c r="BM1" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -628,148 +692,196 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>2.1498</v>
+        <v>0.1666538179386363</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>2.0175</v>
+        <v>0.2430298488733057</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>2.1393</v>
+        <v>0.3167034051366803</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>2.1386</v>
+        <v>0.3813071848293676</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.2558875051605184</v>
+        <v>0.4413158680242198</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.3008607047980171</v>
+        <v>0.5004907344297878</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.3520550477841488</v>
+        <v>0.555955654992267</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.3979740318105338</v>
+        <v>0.6031573833939867</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>0.442116465793928</v>
+        <v>0.6494109625215364</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.4850334938158263</v>
+        <v>0.6999784581679326</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>0.527882852076319</v>
+        <v>0.7462175580918491</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>0.5709951560658442</v>
+        <v>0.787707079769424</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>0.6107058134443879</v>
+        <v>0.822634575189651</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>0.6500566872725951</v>
+        <v>0.8608246083411727</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>0.6853280236002547</v>
+        <v>0.8919736291323209</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>0.7258295854730535</v>
+        <v>0.9098337495769808</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>0.76435826895638</v>
+        <v>0.9435065251585549</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>0.8002061302068085</v>
+        <v>0.9757633104640371</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>0.8332534187568885</v>
+        <v>0.9980502899688698</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>0.8665916084545734</v>
+        <v>1.040809134004379</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>0.8946159179165195</v>
+        <v>1.087869345476759</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>0.9098238024366926</v>
+        <v>1.140509177768562</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>0.9324420923747454</v>
+        <v>1.20150699099647</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>0.9544180487828269</v>
+        <v>1.268174728734792</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>0.9739562806106457</v>
+        <v>1.343680302724072</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>0.9879580110617362</v>
+        <v>1.426622638993372</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>0.9993310423338203</v>
+        <v>1.512822750060887</v>
       </c>
       <c r="AC2" s="1" t="n">
-        <v>1.022056986173751</v>
+        <v>1.612400076798233</v>
       </c>
       <c r="AD2" s="1" t="n">
-        <v>1.047230769697683</v>
+        <v>1.721796362024013</v>
       </c>
       <c r="AE2" s="1" t="n">
-        <v>1.073929252676266</v>
+        <v>1.83143902395037</v>
       </c>
       <c r="AF2" s="1" t="n">
-        <v>1.103664886997665</v>
+        <v>3.9375</v>
       </c>
       <c r="AG2" s="1" t="n">
-        <v>1.136713845172368</v>
+        <v>4.6394</v>
       </c>
       <c r="AH2" s="1" t="n">
-        <v>1.172053309497269</v>
+        <v>4.6934</v>
       </c>
       <c r="AI2" s="1" t="n">
-        <v>1.211220802982266</v>
+        <v>4.7493</v>
       </c>
       <c r="AJ2" s="1" t="n">
-        <v>1.253356408736284</v>
+        <v>4.766</v>
       </c>
       <c r="AK2" s="1" t="n">
-        <v>1.299735350504903</v>
+        <v>4.803</v>
       </c>
       <c r="AL2" s="1" t="n">
-        <v>1.348358786457768</v>
+        <v>4.8222</v>
       </c>
       <c r="AM2" s="1" t="n">
-        <v>1.404461264222284</v>
+        <v>5.3377</v>
       </c>
       <c r="AN2" s="1" t="n">
-        <v>1.463133524841522</v>
+        <v>5.3991</v>
       </c>
       <c r="AO2" s="1" t="n">
-        <v>1.523640891996324</v>
+        <v>6.474</v>
       </c>
       <c r="AP2" s="1" t="n">
-        <v>2.1387</v>
+        <v>8.405799999999999</v>
       </c>
       <c r="AQ2" s="1" t="n">
-        <v>2.0225</v>
+        <v>9.4682</v>
       </c>
       <c r="AR2" s="1" t="n">
-        <v>2.1197</v>
+        <v>9.6045</v>
       </c>
       <c r="AS2" s="1" t="n">
-        <v>2.1425</v>
+        <v>11.2303</v>
       </c>
       <c r="AT2" s="1" t="n">
-        <v>2.0248</v>
+        <v>11.6459</v>
       </c>
       <c r="AU2" s="1" t="n">
-        <v>2.0147</v>
+        <v>12.3557</v>
       </c>
       <c r="AV2" s="1" t="n">
-        <v>2.1372</v>
+        <v>12.6507</v>
       </c>
       <c r="AW2" s="1" t="n">
-        <v>2.201960580843788</v>
+        <v>12.6994</v>
+      </c>
+      <c r="AX2" s="1" t="n">
+        <v>13.3413</v>
+      </c>
+      <c r="AY2" s="1" t="n">
+        <v>13.9538</v>
+      </c>
+      <c r="AZ2" s="1" t="n">
+        <v>14.1276</v>
+      </c>
+      <c r="BA2" s="1" t="n">
+        <v>14.1277</v>
+      </c>
+      <c r="BB2" s="1" t="n">
+        <v>14.1775</v>
+      </c>
+      <c r="BC2" s="1" t="n">
+        <v>14.1775328595</v>
+      </c>
+      <c r="BD2" s="1" t="n">
+        <v>14.6225</v>
+      </c>
+      <c r="BE2" s="1" t="n">
+        <v>14.6266</v>
+      </c>
+      <c r="BF2" s="1" t="n">
+        <v>14.6603</v>
+      </c>
+      <c r="BG2" s="1" t="n">
+        <v>15.1276</v>
+      </c>
+      <c r="BH2" s="1" t="n">
+        <v>15.2338</v>
+      </c>
+      <c r="BI2" s="1" t="n">
+        <v>15.2455</v>
+      </c>
+      <c r="BJ2" s="1" t="n">
+        <v>22.59677898463674</v>
+      </c>
+      <c r="BK2" s="1" t="n">
+        <v>33.49279593850781</v>
+      </c>
+      <c r="BL2" s="1" t="n">
+        <v>49.6428</v>
+      </c>
+      <c r="BM2" s="1" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -779,148 +891,196 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>-0.2418875051605184</v>
+        <v>-1.0524</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>-0.2424875051605184</v>
+        <v>-1.0517</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>-0.2430875051605184</v>
+        <v>-1.0489</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.1862591080036757</v>
+        <v>-1.0474</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-0.2433875051605184</v>
+        <v>-1.044</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>-0.2209875051605184</v>
+        <v>-0.9870999999999999</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.08665910800367582</v>
+        <v>-0.9769000000000001</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>-0.1491875051605184</v>
+        <v>-0.9691000000000001</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-0.2434875051605184</v>
+        <v>-0.9064999999999999</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>-0.2438875051605184</v>
+        <v>-0.9011999999999998</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>-0.2235875051605184</v>
+        <v>-0.8986000000000001</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0.08565910800367571</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>0.05295910800367576</v>
+        <v>-0.8085</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>-0.2045875051605184</v>
+        <v>-0.8066</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>-0.1489875051605184</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>-0.2214875051605184</v>
+        <v>-0.798</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>-0.2413999999999998</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>-0.2237875051605184</v>
+        <v>-0.7345999999999999</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>-0.02660372139363996</v>
+        <v>-0.7326000000000001</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>-0.02038469847299853</v>
+        <v>-0.7307000000000001</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>-0.01674189600865661</v>
+        <v>-0.7290000000000001</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>-0.01391614258328652</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>-0.01140610091752686</v>
+        <v>-0.7222</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>-0.009118963077795958</v>
+        <v>-0.7187000000000001</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>-0.006772381504650434</v>
+        <v>-0.7155999999999998</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>-0.004783032029967913</v>
+        <v>-0.7153</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>0.004016937155439839</v>
+        <v>-0.7151999999999998</v>
       </c>
       <c r="AC3" s="1" t="n">
-        <v>0.005457760810202514</v>
+        <v>-0.6996999999999991</v>
       </c>
       <c r="AD3" s="1" t="n">
-        <v>0.007091904020148686</v>
+        <v>-0.641</v>
       </c>
       <c r="AE3" s="1" t="n">
-        <v>0.009110431180210665</v>
+        <v>-0.6400000000000001</v>
       </c>
       <c r="AF3" s="1" t="n">
-        <v>0.01119925017144392</v>
+        <v>-0.6332959385078141</v>
       </c>
       <c r="AG3" s="1" t="n">
-        <v>0.01380110274233982</v>
+        <v>-0.5684999999999998</v>
       </c>
       <c r="AH3" s="1" t="n">
-        <v>0.01670790887812977</v>
+        <v>-0.5474999999999999</v>
       </c>
       <c r="AI3" s="1" t="n">
-        <v>0.02038615247149913</v>
+        <v>-0.5385</v>
       </c>
       <c r="AJ3" s="1" t="n">
-        <v>0.02770354858855789</v>
+        <v>-0.5352000000000001</v>
       </c>
       <c r="AK3" s="1" t="n">
-        <v>0.1859591080036758</v>
+        <v>-0.5300999999999991</v>
       </c>
       <c r="AL3" s="1" t="n">
-        <v>-0.1490875051605184</v>
+        <v>-0.4580000000000002</v>
       </c>
       <c r="AM3" s="1" t="n">
-        <v>-0.2441875051605184</v>
+        <v>-0.4561000000000002</v>
       </c>
       <c r="AN3" s="1" t="n">
-        <v>-0.2057</v>
+        <v>-0.4550999999999998</v>
       </c>
       <c r="AO3" s="1" t="n">
-        <v>-0.2422</v>
+        <v>-0.03645780975008604</v>
       </c>
       <c r="AP3" s="1" t="n">
-        <v>-0.222</v>
+        <v>-0.02869199521603917</v>
       </c>
       <c r="AQ3" s="1" t="n">
-        <v>0.1201591080036757</v>
+        <v>-0.02294532609048934</v>
       </c>
       <c r="AR3" s="1" t="n">
-        <v>-0.2443875051605184</v>
+        <v>-0.01857056619642398</v>
       </c>
       <c r="AS3" s="1" t="n">
-        <v>-0.2210875051605184</v>
+        <v>-0.01470152817008497</v>
       </c>
       <c r="AT3" s="1" t="n">
-        <v>-0.2210875051605184</v>
+        <v>-0.01113732187417293</v>
       </c>
       <c r="AU3" s="1" t="n">
-        <v>0.1677591080036758</v>
+        <v>-0.008081317477168308</v>
       </c>
       <c r="AV3" s="1" t="n">
-        <v>-0.1215875051605184</v>
+        <v>-0.005492094741752821</v>
       </c>
       <c r="AW3" s="1" t="n">
-        <v>0.05305910800367575</v>
+        <v>0.005492909350871543</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>0.009412284193231493</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>0.01432579185016716</v>
+      </c>
+      <c r="AZ3" s="1" t="n">
+        <v>0.01929323260425074</v>
+      </c>
+      <c r="BA3" s="1" t="n">
+        <v>0.0249057022908134</v>
+      </c>
+      <c r="BB3" s="1" t="n">
+        <v>0.03291651655773845</v>
+      </c>
+      <c r="BC3" s="1" t="n">
+        <v>0.04714091402096572</v>
+      </c>
+      <c r="BD3" s="1" t="n">
+        <v>0.6027609760496304</v>
+      </c>
+      <c r="BE3" s="1" t="n">
+        <v>0.6674609760496302</v>
+      </c>
+      <c r="BF3" s="1" t="n">
+        <v>0.6690609760496304</v>
+      </c>
+      <c r="BG3" s="1" t="n">
+        <v>0.7365609760496303</v>
+      </c>
+      <c r="BH3" s="1" t="n">
+        <v>0.7978609760496305</v>
+      </c>
+      <c r="BI3" s="1" t="n">
+        <v>0.8000609760496302</v>
+      </c>
+      <c r="BJ3" s="1" t="n">
+        <v>0.8079609760496305</v>
+      </c>
+      <c r="BK3" s="1" t="n">
+        <v>1.154404061492187</v>
+      </c>
+      <c r="BL3" s="1" t="n">
+        <v>2.146799999999999</v>
+      </c>
+      <c r="BM3" s="1" t="n">
+        <v>2.551300000000001</v>
       </c>
     </row>
     <row r="4">
@@ -930,148 +1090,196 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>-0.04583772009959415</v>
+        <v>-0.2738</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>-0.04225980531182947</v>
+        <v>-0.2703345475911</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>-0.03813188232877393</v>
+        <v>-0.2635000000000001</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>-0.03526031217609434</v>
+        <v>-0.2534661196629754</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>-0.03190997018874004</v>
+        <v>-0.2409139681005652</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>-0.02814159836227845</v>
+        <v>-0.2259716528153466</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-0.02530573652986316</v>
+        <v>-0.216221645844773</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>-0.02301622629629539</v>
+        <v>-0.2059775827376453</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-0.02112966950406768</v>
+        <v>-0.1948050057547496</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>-0.01908431264203468</v>
+        <v>-0.1844973204690862</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>-0.01689043693066646</v>
+        <v>-0.1760999999999999</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-0.01484628623164569</v>
+        <v>-0.1696880010079219</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>-0.01299541458417611</v>
+        <v>-0.1583832462108734</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>-0.01152161822291867</v>
+        <v>-0.1484275407540106</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>-0.01031056115398229</v>
+        <v>-0.1362488357982355</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>-0.009194889872408409</v>
+        <v>-0.1253489181376701</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>-0.008091153660226126</v>
+        <v>-0.1143361102221089</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-0.007102327510143588</v>
+        <v>-0.1061258440847544</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>-0.005918930050505133</v>
+        <v>-0.1005485227746722</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>-0.004143313640273976</v>
+        <v>-0.09479449661396579</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>-0.002596584635244147</v>
+        <v>-0.08764547700344526</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>0.002377944699176411</v>
+        <v>-0.08127660099721346</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>0.004074272016038512</v>
+        <v>-0.07367353084709713</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>0.00577812294712947</v>
+        <v>-0.06415296090003877</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>0.007087010948013735</v>
+        <v>-0.05489809377263146</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>0.008266065068925502</v>
+        <v>-0.04637989842911205</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>0.009150514043497659</v>
+        <v>-0.03767018966827992</v>
       </c>
       <c r="AC4" s="1" t="n">
-        <v>0.01001542735428408</v>
+        <v>-0.02771061959347916</v>
       </c>
       <c r="AD4" s="1" t="n">
-        <v>0.01147845988114428</v>
+        <v>-0.01782493087238569</v>
       </c>
       <c r="AE4" s="1" t="n">
-        <v>0.01307718860391576</v>
+        <v>-0.01217029443692426</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>0.01500473553071257</v>
+        <v>-0.007264282695126155</v>
       </c>
       <c r="AG4" s="1" t="n">
-        <v>0.01667928687083259</v>
+        <v>-0.003408070401674266</v>
       </c>
       <c r="AH4" s="1" t="n">
-        <v>0.01885885626061543</v>
+        <v>-0.002452230281623512</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>0.02084054766944428</v>
+        <v>0.002775032555469927</v>
       </c>
       <c r="AJ4" s="1" t="n">
-        <v>0.0232968558502127</v>
+        <v>0.007015977544875902</v>
       </c>
       <c r="AK4" s="1" t="n">
-        <v>0.02609477769575542</v>
+        <v>0.01501709539566196</v>
       </c>
       <c r="AL4" s="1" t="n">
-        <v>0.02880518514796288</v>
+        <v>0.02254957654241603</v>
       </c>
       <c r="AM4" s="1" t="n">
-        <v>0.03151266061732404</v>
+        <v>0.030169960378072</v>
       </c>
       <c r="AN4" s="1" t="n">
-        <v>0.0349630852422968</v>
+        <v>0.03763065818796337</v>
       </c>
       <c r="AO4" s="1" t="n">
-        <v>0.03767747406656542</v>
+        <v>0.04713877373521369</v>
       </c>
       <c r="AP4" s="1" t="n">
-        <v>0.03978491792754076</v>
+        <v>0.05678484866889268</v>
       </c>
       <c r="AQ4" s="1" t="n">
-        <v>0.04183770268256063</v>
+        <v>0.06498339592497321</v>
       </c>
       <c r="AR4" s="1" t="n">
-        <v>0.04369012999859814</v>
+        <v>0.07346165864602751</v>
       </c>
       <c r="AS4" s="1" t="n">
-        <v>0.0462216777748123</v>
+        <v>0.08422916751687395</v>
       </c>
       <c r="AT4" s="1" t="n">
-        <v>0.04873255064068729</v>
+        <v>0.09599622850460787</v>
       </c>
       <c r="AU4" s="1" t="n">
-        <v>0.05163070129488657</v>
+        <v>0.1058637373559058</v>
       </c>
       <c r="AV4" s="1" t="n">
-        <v>0.05453743888197017</v>
+        <v>0.115785493248763</v>
       </c>
       <c r="AW4" s="1" t="n">
-        <v>0.05749901212821365</v>
+        <v>0.1265898630746846</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>0.1360246620757213</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>0.1469695369038157</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>0.1533235351925243</v>
+      </c>
+      <c r="BA4" s="1" t="n">
+        <v>0.1608771568416539</v>
+      </c>
+      <c r="BB4" s="1" t="n">
+        <v>0.16770076529122</v>
+      </c>
+      <c r="BC4" s="1" t="n">
+        <v>0.1754228602960284</v>
+      </c>
+      <c r="BD4" s="1" t="n">
+        <v>0.1840592932965428</v>
+      </c>
+      <c r="BE4" s="1" t="n">
+        <v>0.1911460551871733</v>
+      </c>
+      <c r="BF4" s="1" t="n">
+        <v>0.2020953934800419</v>
+      </c>
+      <c r="BG4" s="1" t="n">
+        <v>0.2132302171266567</v>
+      </c>
+      <c r="BH4" s="1" t="n">
+        <v>0.2275430419743145</v>
+      </c>
+      <c r="BI4" s="1" t="n">
+        <v>0.2336200620286646</v>
+      </c>
+      <c r="BJ4" s="1" t="n">
+        <v>0.2346200620286645</v>
+      </c>
+      <c r="BK4" s="1" t="n">
+        <v>0.2412593412843335</v>
+      </c>
+      <c r="BL4" s="1" t="n">
+        <v>0.2551172296748787</v>
+      </c>
+      <c r="BM4" s="1" t="n">
+        <v>0.2700358056145989</v>
       </c>
     </row>
   </sheetData>
